--- a/sample_data/insurance_sample.xlsx
+++ b/sample_data/insurance_sample.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Insurance" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="196">
   <si>
     <t>policy_id</t>
   </si>
@@ -58,9 +58,192 @@
     <t>P004</t>
   </si>
   <si>
+    <t>P005</t>
+  </si>
+  <si>
     <t>P006</t>
   </si>
   <si>
+    <t>P007</t>
+  </si>
+  <si>
+    <t>P008</t>
+  </si>
+  <si>
+    <t>P009</t>
+  </si>
+  <si>
+    <t>P010</t>
+  </si>
+  <si>
+    <t>P011</t>
+  </si>
+  <si>
+    <t>P012</t>
+  </si>
+  <si>
+    <t>P013</t>
+  </si>
+  <si>
+    <t>P014</t>
+  </si>
+  <si>
+    <t>P015</t>
+  </si>
+  <si>
+    <t>P016</t>
+  </si>
+  <si>
+    <t>P017</t>
+  </si>
+  <si>
+    <t>P018</t>
+  </si>
+  <si>
+    <t>P019</t>
+  </si>
+  <si>
+    <t>P020</t>
+  </si>
+  <si>
+    <t>P021</t>
+  </si>
+  <si>
+    <t>P022</t>
+  </si>
+  <si>
+    <t>P023</t>
+  </si>
+  <si>
+    <t>P024</t>
+  </si>
+  <si>
+    <t>P025</t>
+  </si>
+  <si>
+    <t>P026</t>
+  </si>
+  <si>
+    <t>P027</t>
+  </si>
+  <si>
+    <t>P028</t>
+  </si>
+  <si>
+    <t>P029</t>
+  </si>
+  <si>
+    <t>P030</t>
+  </si>
+  <si>
+    <t>P031</t>
+  </si>
+  <si>
+    <t>P032</t>
+  </si>
+  <si>
+    <t>P033</t>
+  </si>
+  <si>
+    <t>P034</t>
+  </si>
+  <si>
+    <t>P035</t>
+  </si>
+  <si>
+    <t>P036</t>
+  </si>
+  <si>
+    <t>P037</t>
+  </si>
+  <si>
+    <t>P038</t>
+  </si>
+  <si>
+    <t>P039</t>
+  </si>
+  <si>
+    <t>P040</t>
+  </si>
+  <si>
+    <t>P041</t>
+  </si>
+  <si>
+    <t>P042</t>
+  </si>
+  <si>
+    <t>P043</t>
+  </si>
+  <si>
+    <t>P044</t>
+  </si>
+  <si>
+    <t>P045</t>
+  </si>
+  <si>
+    <t>P046</t>
+  </si>
+  <si>
+    <t>P047</t>
+  </si>
+  <si>
+    <t>P048</t>
+  </si>
+  <si>
+    <t>P049</t>
+  </si>
+  <si>
+    <t>P050</t>
+  </si>
+  <si>
+    <t>P051</t>
+  </si>
+  <si>
+    <t>P052</t>
+  </si>
+  <si>
+    <t>P053</t>
+  </si>
+  <si>
+    <t>P054</t>
+  </si>
+  <si>
+    <t>P055</t>
+  </si>
+  <si>
+    <t>P056</t>
+  </si>
+  <si>
+    <t>P057</t>
+  </si>
+  <si>
+    <t>P058</t>
+  </si>
+  <si>
+    <t>P059</t>
+  </si>
+  <si>
+    <t>P060</t>
+  </si>
+  <si>
+    <t>P061</t>
+  </si>
+  <si>
+    <t>P062</t>
+  </si>
+  <si>
+    <t>P063</t>
+  </si>
+  <si>
+    <t>P064</t>
+  </si>
+  <si>
+    <t>P065</t>
+  </si>
+  <si>
+    <t>P066</t>
+  </si>
+  <si>
     <t>Auto</t>
   </si>
   <si>
@@ -70,16 +253,25 @@
     <t>Santé</t>
   </si>
   <si>
+    <t>Entreprise</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
     <t>Abidjan</t>
   </si>
   <si>
     <t>Bouaké</t>
   </si>
   <si>
-    <t>ABIDJAN</t>
-  </si>
-  <si>
-    <t>S001</t>
+    <t>Yamoussoukro</t>
+  </si>
+  <si>
+    <t>Korhogo</t>
+  </si>
+  <si>
+    <t>San-Pédro</t>
   </si>
   <si>
     <t>S002</t>
@@ -88,19 +280,328 @@
     <t>S003</t>
   </si>
   <si>
+    <t>S005</t>
+  </si>
+  <si>
+    <t>S006</t>
+  </si>
+  <si>
+    <t>S008</t>
+  </si>
+  <si>
+    <t>S009</t>
+  </si>
+  <si>
+    <t>S011</t>
+  </si>
+  <si>
+    <t>S012</t>
+  </si>
+  <si>
+    <t>S014</t>
+  </si>
+  <si>
+    <t>S015</t>
+  </si>
+  <si>
+    <t>S017</t>
+  </si>
+  <si>
+    <t>S018</t>
+  </si>
+  <si>
+    <t>S020</t>
+  </si>
+  <si>
+    <t>S021</t>
+  </si>
+  <si>
+    <t>S023</t>
+  </si>
+  <si>
+    <t>S024</t>
+  </si>
+  <si>
+    <t>S026</t>
+  </si>
+  <si>
+    <t>S027</t>
+  </si>
+  <si>
+    <t>S029</t>
+  </si>
+  <si>
+    <t>S030</t>
+  </si>
+  <si>
+    <t>S032</t>
+  </si>
+  <si>
+    <t>S033</t>
+  </si>
+  <si>
+    <t>S035</t>
+  </si>
+  <si>
+    <t>S036</t>
+  </si>
+  <si>
+    <t>S038</t>
+  </si>
+  <si>
+    <t>S039</t>
+  </si>
+  <si>
+    <t>S041</t>
+  </si>
+  <si>
+    <t>S042</t>
+  </si>
+  <si>
+    <t>S044</t>
+  </si>
+  <si>
+    <t>S045</t>
+  </si>
+  <si>
+    <t>S047</t>
+  </si>
+  <si>
+    <t>S048</t>
+  </si>
+  <si>
+    <t>S050</t>
+  </si>
+  <si>
+    <t>S051</t>
+  </si>
+  <si>
+    <t>S053</t>
+  </si>
+  <si>
+    <t>S054</t>
+  </si>
+  <si>
+    <t>S056</t>
+  </si>
+  <si>
+    <t>S057</t>
+  </si>
+  <si>
+    <t>S059</t>
+  </si>
+  <si>
+    <t>S060</t>
+  </si>
+  <si>
+    <t>S062</t>
+  </si>
+  <si>
+    <t>S063</t>
+  </si>
+  <si>
+    <t>S065</t>
+  </si>
+  <si>
+    <t>S066</t>
+  </si>
+  <si>
     <t>2026-01-01</t>
   </si>
   <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>2026-02-01</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>2026-06-06</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-10-10</t>
+  </si>
+  <si>
+    <t>2026-11-11</t>
+  </si>
+  <si>
+    <t>2026-12-12</t>
+  </si>
+  <si>
+    <t>2026-01-13</t>
+  </si>
+  <si>
+    <t>2026-02-14</t>
   </si>
   <si>
     <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-10-22</t>
+  </si>
+  <si>
+    <t>2026-11-23</t>
+  </si>
+  <si>
+    <t>2026-12-24</t>
+  </si>
+  <si>
+    <t>2026-01-25</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>2026-10-07</t>
+  </si>
+  <si>
+    <t>2026-11-08</t>
+  </si>
+  <si>
+    <t>2026-12-09</t>
+  </si>
+  <si>
+    <t>2026-01-10</t>
+  </si>
+  <si>
+    <t>2026-02-11</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-10-19</t>
+  </si>
+  <si>
+    <t>2026-11-20</t>
+  </si>
+  <si>
+    <t>2026-12-21</t>
+  </si>
+  <si>
+    <t>2026-01-22</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-10-04</t>
+  </si>
+  <si>
+    <t>2026-11-05</t>
+  </si>
+  <si>
+    <t>2026-12-06</t>
+  </si>
+  <si>
+    <t>2026-01-07</t>
+  </si>
+  <si>
+    <t>2026-02-08</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
   </si>
 </sst>
 </file>
@@ -458,7 +959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -498,28 +999,28 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D2">
-        <v>150000</v>
+        <v>87500</v>
       </c>
       <c r="E2">
-        <v>145000</v>
+        <v>85000</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>8750</v>
       </c>
       <c r="I2">
-        <v>135000</v>
+        <v>78750</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -527,31 +1028,31 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="D3">
-        <v>210000</v>
+        <v>95000</v>
       </c>
       <c r="E3">
-        <v>200000</v>
+        <v>90000</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="G3">
-        <v>350000</v>
+        <v>50000</v>
       </c>
       <c r="H3">
-        <v>21000</v>
+        <v>9500</v>
       </c>
       <c r="I3">
-        <v>189000</v>
+        <v>85500</v>
       </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -559,31 +1060,31 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="D4">
-        <v>90000</v>
+        <v>102500</v>
       </c>
       <c r="E4">
-        <v>90000</v>
+        <v>95000</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="G4">
-        <v>45000</v>
+        <v>62500</v>
       </c>
       <c r="H4">
-        <v>9000</v>
+        <v>10250</v>
       </c>
       <c r="I4">
-        <v>81000</v>
+        <v>92250</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -591,83 +1092,2064 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="D5">
-        <v>300000</v>
+        <v>110000</v>
       </c>
       <c r="E5">
-        <v>270000</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
+        <v>100000</v>
       </c>
       <c r="G5">
-        <v>1250000</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>45000</v>
+        <v>11000</v>
       </c>
       <c r="I5">
-        <v>255000</v>
+        <v>99000</v>
       </c>
       <c r="J5" t="s">
-        <v>27</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="D6">
-        <v>300000</v>
+        <v>117500</v>
       </c>
       <c r="E6">
-        <v>270000</v>
+        <v>117500</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="G6">
-        <v>1250000</v>
+        <v>87500</v>
       </c>
       <c r="H6">
-        <v>45000</v>
+        <v>11750</v>
       </c>
       <c r="I6">
-        <v>255000</v>
+        <v>105750</v>
       </c>
       <c r="J6" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7">
+        <v>125000</v>
+      </c>
+      <c r="E7">
+        <v>122500</v>
+      </c>
+      <c r="F7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7">
+        <v>100000</v>
+      </c>
+      <c r="H7">
+        <v>12500</v>
+      </c>
+      <c r="I7">
+        <v>112500</v>
+      </c>
+      <c r="J7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8">
+        <v>132500</v>
+      </c>
+      <c r="E8">
+        <v>127500</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>13250</v>
+      </c>
+      <c r="I8">
+        <v>119250</v>
+      </c>
+      <c r="J8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="D7">
+      <c r="B9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9">
+        <v>140000</v>
+      </c>
+      <c r="E9">
+        <v>132500</v>
+      </c>
+      <c r="F9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9">
+        <v>125000</v>
+      </c>
+      <c r="H9">
+        <v>14000</v>
+      </c>
+      <c r="I9">
+        <v>126000</v>
+      </c>
+      <c r="J9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10">
+        <v>147500</v>
+      </c>
+      <c r="E10">
+        <v>137500</v>
+      </c>
+      <c r="F10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10">
+        <v>137500</v>
+      </c>
+      <c r="H10">
+        <v>14750</v>
+      </c>
+      <c r="I10">
+        <v>132750</v>
+      </c>
+      <c r="J10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11">
+        <v>155000</v>
+      </c>
+      <c r="E11">
+        <v>155000</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>15500</v>
+      </c>
+      <c r="I11">
+        <v>139500</v>
+      </c>
+      <c r="J11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12">
+        <v>162500</v>
+      </c>
+      <c r="E12">
+        <v>160000</v>
+      </c>
+      <c r="F12" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12">
+        <v>162500</v>
+      </c>
+      <c r="H12">
+        <v>16250</v>
+      </c>
+      <c r="I12">
+        <v>146250</v>
+      </c>
+      <c r="J12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13">
+        <v>170000</v>
+      </c>
+      <c r="E13">
+        <v>165000</v>
+      </c>
+      <c r="F13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13">
+        <v>175000</v>
+      </c>
+      <c r="H13">
+        <v>17000</v>
+      </c>
+      <c r="I13">
+        <v>153000</v>
+      </c>
+      <c r="J13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14">
+        <v>177500</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>17750</v>
+      </c>
+      <c r="I14">
+        <v>159750</v>
+      </c>
+      <c r="J14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15">
+        <v>185000</v>
+      </c>
+      <c r="E15">
+        <v>175000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15">
+        <v>200000</v>
+      </c>
+      <c r="H15">
+        <v>18500</v>
+      </c>
+      <c r="I15">
+        <v>166500</v>
+      </c>
+      <c r="J15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16">
+        <v>192500</v>
+      </c>
+      <c r="E16">
+        <v>192500</v>
+      </c>
+      <c r="F16" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16">
+        <v>212500</v>
+      </c>
+      <c r="H16">
+        <v>19250</v>
+      </c>
+      <c r="I16">
+        <v>173250</v>
+      </c>
+      <c r="J16" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17">
+        <v>200000</v>
+      </c>
+      <c r="E17">
+        <v>197500</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>20000</v>
+      </c>
+      <c r="I17">
         <v>180000</v>
       </c>
-      <c r="H7">
-        <v>18000</v>
-      </c>
-      <c r="I7">
-        <v>162000</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="J17" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18">
+        <v>207500</v>
+      </c>
+      <c r="E18">
+        <v>202500</v>
+      </c>
+      <c r="F18" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18">
+        <v>20750</v>
+      </c>
+      <c r="I18">
+        <v>186750</v>
+      </c>
+      <c r="J18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19">
+        <v>215000</v>
+      </c>
+      <c r="E19">
+        <v>207500</v>
+      </c>
+      <c r="F19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G19">
+        <v>250000</v>
+      </c>
+      <c r="H19">
+        <v>21500</v>
+      </c>
+      <c r="I19">
+        <v>193500</v>
+      </c>
+      <c r="J19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
         <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20">
+        <v>222500</v>
+      </c>
+      <c r="E20">
+        <v>212500</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>22250</v>
+      </c>
+      <c r="I20">
+        <v>200250</v>
+      </c>
+      <c r="J20" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21">
+        <v>230000</v>
+      </c>
+      <c r="E21">
+        <v>230000</v>
+      </c>
+      <c r="F21" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21">
+        <v>275000</v>
+      </c>
+      <c r="H21">
+        <v>23000</v>
+      </c>
+      <c r="I21">
+        <v>207000</v>
+      </c>
+      <c r="J21" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22">
+        <v>237500</v>
+      </c>
+      <c r="E22">
+        <v>235000</v>
+      </c>
+      <c r="F22" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22">
+        <v>287500</v>
+      </c>
+      <c r="H22">
+        <v>23750</v>
+      </c>
+      <c r="I22">
+        <v>213750</v>
+      </c>
+      <c r="J22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23">
+        <v>245000</v>
+      </c>
+      <c r="E23">
+        <v>240000</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>24500</v>
+      </c>
+      <c r="I23">
+        <v>220500</v>
+      </c>
+      <c r="J23" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24">
+        <v>252500</v>
+      </c>
+      <c r="E24">
+        <v>245000</v>
+      </c>
+      <c r="F24" t="s">
+        <v>100</v>
+      </c>
+      <c r="G24">
+        <v>312500</v>
+      </c>
+      <c r="H24">
+        <v>25250</v>
+      </c>
+      <c r="I24">
+        <v>227250</v>
+      </c>
+      <c r="J24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25">
+        <v>260000</v>
+      </c>
+      <c r="E25">
+        <v>250000</v>
+      </c>
+      <c r="F25" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25">
+        <v>325000</v>
+      </c>
+      <c r="H25">
+        <v>26000</v>
+      </c>
+      <c r="I25">
+        <v>234000</v>
+      </c>
+      <c r="J25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26">
+        <v>267500</v>
+      </c>
+      <c r="E26">
+        <v>267500</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>26750</v>
+      </c>
+      <c r="I26">
+        <v>240750</v>
+      </c>
+      <c r="J26" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27">
+        <v>275000</v>
+      </c>
+      <c r="F27" t="s">
+        <v>102</v>
+      </c>
+      <c r="G27">
+        <v>350000</v>
+      </c>
+      <c r="H27">
+        <v>27500</v>
+      </c>
+      <c r="I27">
+        <v>247500</v>
+      </c>
+      <c r="J27" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28">
+        <v>282500</v>
+      </c>
+      <c r="E28">
+        <v>277500</v>
+      </c>
+      <c r="F28" t="s">
+        <v>103</v>
+      </c>
+      <c r="G28">
+        <v>362500</v>
+      </c>
+      <c r="H28">
+        <v>28250</v>
+      </c>
+      <c r="I28">
+        <v>254250</v>
+      </c>
+      <c r="J28" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29">
+        <v>290000</v>
+      </c>
+      <c r="E29">
+        <v>282500</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>29000</v>
+      </c>
+      <c r="I29">
+        <v>261000</v>
+      </c>
+      <c r="J29" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30">
+        <v>297500</v>
+      </c>
+      <c r="E30">
+        <v>287500</v>
+      </c>
+      <c r="F30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G30">
+        <v>387500</v>
+      </c>
+      <c r="H30">
+        <v>29750</v>
+      </c>
+      <c r="I30">
+        <v>267750</v>
+      </c>
+      <c r="J30" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31">
+        <v>305000</v>
+      </c>
+      <c r="E31">
+        <v>305000</v>
+      </c>
+      <c r="F31" t="s">
+        <v>105</v>
+      </c>
+      <c r="G31">
+        <v>400000</v>
+      </c>
+      <c r="H31">
+        <v>30500</v>
+      </c>
+      <c r="I31">
+        <v>274500</v>
+      </c>
+      <c r="J31" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32">
+        <v>312500</v>
+      </c>
+      <c r="E32">
+        <v>310000</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>31250</v>
+      </c>
+      <c r="I32">
+        <v>281250</v>
+      </c>
+      <c r="J32" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33">
+        <v>320000</v>
+      </c>
+      <c r="E33">
+        <v>315000</v>
+      </c>
+      <c r="F33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G33">
+        <v>425000</v>
+      </c>
+      <c r="H33">
+        <v>32000</v>
+      </c>
+      <c r="I33">
+        <v>288000</v>
+      </c>
+      <c r="J33" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34">
+        <v>327500</v>
+      </c>
+      <c r="E34">
+        <v>320000</v>
+      </c>
+      <c r="F34" t="s">
+        <v>107</v>
+      </c>
+      <c r="G34">
+        <v>437500</v>
+      </c>
+      <c r="H34">
+        <v>32750</v>
+      </c>
+      <c r="I34">
+        <v>294750</v>
+      </c>
+      <c r="J34" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35">
+        <v>335000</v>
+      </c>
+      <c r="E35">
+        <v>325000</v>
+      </c>
+      <c r="H35">
+        <v>33500</v>
+      </c>
+      <c r="I35">
+        <v>301500</v>
+      </c>
+      <c r="J35" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" t="s">
+        <v>85</v>
+      </c>
+      <c r="D36">
+        <v>342500</v>
+      </c>
+      <c r="E36">
+        <v>342500</v>
+      </c>
+      <c r="F36" t="s">
+        <v>108</v>
+      </c>
+      <c r="G36">
+        <v>462500</v>
+      </c>
+      <c r="H36">
+        <v>34250</v>
+      </c>
+      <c r="I36">
+        <v>308250</v>
+      </c>
+      <c r="J36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37">
+        <v>350000</v>
+      </c>
+      <c r="E37">
+        <v>347500</v>
+      </c>
+      <c r="F37" t="s">
+        <v>109</v>
+      </c>
+      <c r="G37">
+        <v>475000</v>
+      </c>
+      <c r="H37">
+        <v>35000</v>
+      </c>
+      <c r="I37">
+        <v>315000</v>
+      </c>
+      <c r="J37" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" t="s">
+        <v>82</v>
+      </c>
+      <c r="D38">
+        <v>357500</v>
+      </c>
+      <c r="E38">
+        <v>352500</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>35750</v>
+      </c>
+      <c r="I38">
+        <v>321750</v>
+      </c>
+      <c r="J38" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39">
+        <v>365000</v>
+      </c>
+      <c r="E39">
+        <v>357500</v>
+      </c>
+      <c r="F39" t="s">
+        <v>110</v>
+      </c>
+      <c r="G39">
+        <v>500000</v>
+      </c>
+      <c r="H39">
+        <v>36500</v>
+      </c>
+      <c r="I39">
+        <v>328500</v>
+      </c>
+      <c r="J39" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40">
+        <v>372500</v>
+      </c>
+      <c r="F40" t="s">
+        <v>111</v>
+      </c>
+      <c r="G40">
+        <v>512500</v>
+      </c>
+      <c r="H40">
+        <v>37250</v>
+      </c>
+      <c r="I40">
+        <v>335250</v>
+      </c>
+      <c r="J40" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41">
+        <v>380000</v>
+      </c>
+      <c r="E41">
+        <v>380000</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>38000</v>
+      </c>
+      <c r="I41">
+        <v>342000</v>
+      </c>
+      <c r="J41" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42">
+        <v>387500</v>
+      </c>
+      <c r="E42">
+        <v>385000</v>
+      </c>
+      <c r="F42" t="s">
+        <v>112</v>
+      </c>
+      <c r="G42">
+        <v>537500</v>
+      </c>
+      <c r="H42">
+        <v>38750</v>
+      </c>
+      <c r="I42">
+        <v>348750</v>
+      </c>
+      <c r="J42" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D43">
+        <v>395000</v>
+      </c>
+      <c r="E43">
+        <v>390000</v>
+      </c>
+      <c r="F43" t="s">
+        <v>113</v>
+      </c>
+      <c r="G43">
+        <v>550000</v>
+      </c>
+      <c r="H43">
+        <v>39500</v>
+      </c>
+      <c r="I43">
+        <v>355500</v>
+      </c>
+      <c r="J43" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44">
+        <v>402500</v>
+      </c>
+      <c r="E44">
+        <v>395000</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>40250</v>
+      </c>
+      <c r="I44">
+        <v>362250</v>
+      </c>
+      <c r="J44" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" t="s">
+        <v>84</v>
+      </c>
+      <c r="D45">
+        <v>410000</v>
+      </c>
+      <c r="E45">
+        <v>400000</v>
+      </c>
+      <c r="F45" t="s">
+        <v>114</v>
+      </c>
+      <c r="G45">
+        <v>575000</v>
+      </c>
+      <c r="H45">
+        <v>41000</v>
+      </c>
+      <c r="I45">
+        <v>369000</v>
+      </c>
+      <c r="J45" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" t="s">
+        <v>85</v>
+      </c>
+      <c r="D46">
+        <v>417500</v>
+      </c>
+      <c r="E46">
+        <v>417500</v>
+      </c>
+      <c r="F46" t="s">
+        <v>115</v>
+      </c>
+      <c r="G46">
+        <v>587500</v>
+      </c>
+      <c r="H46">
+        <v>41750</v>
+      </c>
+      <c r="I46">
+        <v>375750</v>
+      </c>
+      <c r="J46" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" t="s">
+        <v>76</v>
+      </c>
+      <c r="C47" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47">
+        <v>425000</v>
+      </c>
+      <c r="E47">
+        <v>422500</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>42500</v>
+      </c>
+      <c r="I47">
+        <v>382500</v>
+      </c>
+      <c r="J47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" t="s">
+        <v>82</v>
+      </c>
+      <c r="D48">
+        <v>432500</v>
+      </c>
+      <c r="E48">
+        <v>427500</v>
+      </c>
+      <c r="F48" t="s">
+        <v>116</v>
+      </c>
+      <c r="G48">
+        <v>612500</v>
+      </c>
+      <c r="H48">
+        <v>43250</v>
+      </c>
+      <c r="I48">
+        <v>389250</v>
+      </c>
+      <c r="J48" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49" t="s">
+        <v>83</v>
+      </c>
+      <c r="D49">
+        <v>440000</v>
+      </c>
+      <c r="E49">
+        <v>432500</v>
+      </c>
+      <c r="F49" t="s">
+        <v>117</v>
+      </c>
+      <c r="G49">
+        <v>625000</v>
+      </c>
+      <c r="H49">
+        <v>44000</v>
+      </c>
+      <c r="I49">
+        <v>396000</v>
+      </c>
+      <c r="J49" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" t="s">
+        <v>84</v>
+      </c>
+      <c r="D50">
+        <v>447500</v>
+      </c>
+      <c r="E50">
+        <v>437500</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>44750</v>
+      </c>
+      <c r="I50">
+        <v>402750</v>
+      </c>
+      <c r="J50" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" t="s">
+        <v>80</v>
+      </c>
+      <c r="D51">
+        <v>455000</v>
+      </c>
+      <c r="E51">
+        <v>455000</v>
+      </c>
+      <c r="F51" t="s">
+        <v>118</v>
+      </c>
+      <c r="G51">
+        <v>650000</v>
+      </c>
+      <c r="H51">
+        <v>45500</v>
+      </c>
+      <c r="I51">
+        <v>409500</v>
+      </c>
+      <c r="J51" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" t="s">
+        <v>76</v>
+      </c>
+      <c r="C52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D52">
+        <v>462500</v>
+      </c>
+      <c r="E52">
+        <v>460000</v>
+      </c>
+      <c r="F52" t="s">
+        <v>119</v>
+      </c>
+      <c r="H52">
+        <v>46250</v>
+      </c>
+      <c r="I52">
+        <v>416250</v>
+      </c>
+      <c r="J52" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" t="s">
+        <v>77</v>
+      </c>
+      <c r="C53" t="s">
+        <v>82</v>
+      </c>
+      <c r="D53">
+        <v>470000</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>47000</v>
+      </c>
+      <c r="I53">
+        <v>423000</v>
+      </c>
+      <c r="J53" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" t="s">
+        <v>83</v>
+      </c>
+      <c r="D54">
+        <v>477500</v>
+      </c>
+      <c r="E54">
+        <v>470000</v>
+      </c>
+      <c r="F54" t="s">
+        <v>120</v>
+      </c>
+      <c r="G54">
+        <v>687500</v>
+      </c>
+      <c r="H54">
+        <v>47750</v>
+      </c>
+      <c r="I54">
+        <v>429750</v>
+      </c>
+      <c r="J54" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" t="s">
+        <v>79</v>
+      </c>
+      <c r="C55" t="s">
+        <v>84</v>
+      </c>
+      <c r="D55">
+        <v>485000</v>
+      </c>
+      <c r="E55">
+        <v>475000</v>
+      </c>
+      <c r="F55" t="s">
+        <v>121</v>
+      </c>
+      <c r="G55">
+        <v>700000</v>
+      </c>
+      <c r="H55">
+        <v>48500</v>
+      </c>
+      <c r="I55">
+        <v>436500</v>
+      </c>
+      <c r="J55" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C56" t="s">
+        <v>85</v>
+      </c>
+      <c r="D56">
+        <v>492500</v>
+      </c>
+      <c r="E56">
+        <v>492500</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>49250</v>
+      </c>
+      <c r="I56">
+        <v>443250</v>
+      </c>
+      <c r="J56" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57" t="s">
+        <v>81</v>
+      </c>
+      <c r="D57">
+        <v>500000</v>
+      </c>
+      <c r="E57">
+        <v>497500</v>
+      </c>
+      <c r="F57" t="s">
+        <v>122</v>
+      </c>
+      <c r="G57">
+        <v>725000</v>
+      </c>
+      <c r="H57">
+        <v>50000</v>
+      </c>
+      <c r="I57">
+        <v>450000</v>
+      </c>
+      <c r="J57" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" t="s">
+        <v>77</v>
+      </c>
+      <c r="C58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D58">
+        <v>507500</v>
+      </c>
+      <c r="E58">
+        <v>502500</v>
+      </c>
+      <c r="F58" t="s">
+        <v>123</v>
+      </c>
+      <c r="G58">
+        <v>737500</v>
+      </c>
+      <c r="H58">
+        <v>50750</v>
+      </c>
+      <c r="I58">
+        <v>456750</v>
+      </c>
+      <c r="J58" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" t="s">
+        <v>78</v>
+      </c>
+      <c r="C59" t="s">
+        <v>83</v>
+      </c>
+      <c r="D59">
+        <v>515000</v>
+      </c>
+      <c r="E59">
+        <v>507500</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>51500</v>
+      </c>
+      <c r="I59">
+        <v>463500</v>
+      </c>
+      <c r="J59" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" t="s">
+        <v>79</v>
+      </c>
+      <c r="C60" t="s">
+        <v>84</v>
+      </c>
+      <c r="D60">
+        <v>522500</v>
+      </c>
+      <c r="E60">
+        <v>512500</v>
+      </c>
+      <c r="F60" t="s">
+        <v>124</v>
+      </c>
+      <c r="G60">
+        <v>762500</v>
+      </c>
+      <c r="H60">
+        <v>52250</v>
+      </c>
+      <c r="I60">
+        <v>470250</v>
+      </c>
+      <c r="J60" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" t="s">
+        <v>80</v>
+      </c>
+      <c r="D61">
+        <v>530000</v>
+      </c>
+      <c r="E61">
+        <v>530000</v>
+      </c>
+      <c r="F61" t="s">
+        <v>125</v>
+      </c>
+      <c r="G61">
+        <v>775000</v>
+      </c>
+      <c r="H61">
+        <v>53000</v>
+      </c>
+      <c r="I61">
+        <v>477000</v>
+      </c>
+      <c r="J61" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" t="s">
+        <v>76</v>
+      </c>
+      <c r="C62" t="s">
+        <v>81</v>
+      </c>
+      <c r="D62">
+        <v>537500</v>
+      </c>
+      <c r="E62">
+        <v>535000</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>53750</v>
+      </c>
+      <c r="I62">
+        <v>483750</v>
+      </c>
+      <c r="J62" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" t="s">
+        <v>77</v>
+      </c>
+      <c r="C63" t="s">
+        <v>82</v>
+      </c>
+      <c r="D63">
+        <v>545000</v>
+      </c>
+      <c r="E63">
+        <v>540000</v>
+      </c>
+      <c r="F63" t="s">
+        <v>126</v>
+      </c>
+      <c r="G63">
+        <v>800000</v>
+      </c>
+      <c r="H63">
+        <v>54500</v>
+      </c>
+      <c r="I63">
+        <v>490500</v>
+      </c>
+      <c r="J63" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" t="s">
+        <v>78</v>
+      </c>
+      <c r="C64" t="s">
+        <v>83</v>
+      </c>
+      <c r="D64">
+        <v>552500</v>
+      </c>
+      <c r="E64">
+        <v>545000</v>
+      </c>
+      <c r="F64" t="s">
+        <v>127</v>
+      </c>
+      <c r="G64">
+        <v>812500</v>
+      </c>
+      <c r="H64">
+        <v>55250</v>
+      </c>
+      <c r="I64">
+        <v>497250</v>
+      </c>
+      <c r="J64" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" t="s">
+        <v>79</v>
+      </c>
+      <c r="C65" t="s">
+        <v>84</v>
+      </c>
+      <c r="D65">
+        <v>560000</v>
+      </c>
+      <c r="E65">
+        <v>550000</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>56000</v>
+      </c>
+      <c r="I65">
+        <v>504000</v>
+      </c>
+      <c r="J65" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" t="s">
+        <v>80</v>
+      </c>
+      <c r="C66" t="s">
+        <v>85</v>
+      </c>
+      <c r="D66">
+        <v>567500</v>
+      </c>
+      <c r="F66" t="s">
+        <v>128</v>
+      </c>
+      <c r="G66">
+        <v>837500</v>
+      </c>
+      <c r="H66">
+        <v>56750</v>
+      </c>
+      <c r="I66">
+        <v>510750</v>
+      </c>
+      <c r="J66" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" t="s">
+        <v>76</v>
+      </c>
+      <c r="C67" t="s">
+        <v>81</v>
+      </c>
+      <c r="D67">
+        <v>575000</v>
+      </c>
+      <c r="E67">
+        <v>572500</v>
+      </c>
+      <c r="F67" t="s">
+        <v>129</v>
+      </c>
+      <c r="G67">
+        <v>850000</v>
+      </c>
+      <c r="H67">
+        <v>57500</v>
+      </c>
+      <c r="I67">
+        <v>517500</v>
+      </c>
+      <c r="J67" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" t="s">
+        <v>13</v>
+      </c>
+      <c r="B68" t="s">
+        <v>79</v>
+      </c>
+      <c r="C68" t="s">
+        <v>84</v>
+      </c>
+      <c r="D68">
+        <v>110000</v>
+      </c>
+      <c r="E68">
+        <v>100000</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>11000</v>
+      </c>
+      <c r="I68">
+        <v>99000</v>
+      </c>
+      <c r="J68" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" t="s">
+        <v>21</v>
+      </c>
+      <c r="B69" t="s">
+        <v>77</v>
+      </c>
+      <c r="C69" t="s">
+        <v>82</v>
+      </c>
+      <c r="D69">
+        <v>170000</v>
+      </c>
+      <c r="E69">
+        <v>165000</v>
+      </c>
+      <c r="F69" t="s">
+        <v>93</v>
+      </c>
+      <c r="G69">
+        <v>175000</v>
+      </c>
+      <c r="H69">
+        <v>17000</v>
+      </c>
+      <c r="I69">
+        <v>153000</v>
+      </c>
+      <c r="J69" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" t="s">
+        <v>36</v>
+      </c>
+      <c r="B70" t="s">
+        <v>77</v>
+      </c>
+      <c r="C70" t="s">
+        <v>82</v>
+      </c>
+      <c r="D70">
+        <v>282500</v>
+      </c>
+      <c r="E70">
+        <v>277500</v>
+      </c>
+      <c r="F70" t="s">
+        <v>103</v>
+      </c>
+      <c r="G70">
+        <v>362500</v>
+      </c>
+      <c r="H70">
+        <v>28250</v>
+      </c>
+      <c r="I70">
+        <v>254250</v>
+      </c>
+      <c r="J70" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" t="s">
+        <v>50</v>
+      </c>
+      <c r="B71" t="s">
+        <v>76</v>
+      </c>
+      <c r="C71" t="s">
+        <v>81</v>
+      </c>
+      <c r="D71">
+        <v>387500</v>
+      </c>
+      <c r="E71">
+        <v>385000</v>
+      </c>
+      <c r="F71" t="s">
+        <v>112</v>
+      </c>
+      <c r="G71">
+        <v>537500</v>
+      </c>
+      <c r="H71">
+        <v>38750</v>
+      </c>
+      <c r="I71">
+        <v>348750</v>
+      </c>
+      <c r="J71" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" t="s">
+        <v>64</v>
+      </c>
+      <c r="B72" t="s">
+        <v>80</v>
+      </c>
+      <c r="C72" t="s">
+        <v>85</v>
+      </c>
+      <c r="D72">
+        <v>492500</v>
+      </c>
+      <c r="E72">
+        <v>492500</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>49250</v>
+      </c>
+      <c r="I72">
+        <v>443250</v>
+      </c>
+      <c r="J72" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
